--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260803.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>152,735</t>
+          <t>151,885</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.81%</t>
+          <t>28.46%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.31%</t>
+          <t>8.33%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>110,550</t>
+          <t>110,050</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>7.46%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>134,845</t>
+          <t>133,945</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>56,295</t>
+          <t>56,025</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.12%</t>
+          <t>5.19%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>66,220</t>
+          <t>65,770</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>73,005</t>
+          <t>72,405</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>50,435</t>
+          <t>50,035</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>2.97%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,995</t>
+          <t>21,825</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,363</t>
+          <t>20,233</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,110</t>
+          <t>34,860</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,595</t>
+          <t>22,445</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>85,365</t>
+          <t>84,905</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>56,845</t>
+          <t>56,495</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>21,690</t>
+          <t>21,570</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>29,548</t>
+          <t>29,348</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>40,290</t>
+          <t>40,070</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1007,56 +1007,56 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,058</t>
+          <t>65,698</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>89,356,605</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>12,851</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1073,56 +1073,56 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,698</t>
+          <t>23,568</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>12,951</t>
+          <t>140,445</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>141,205</t>
+          <t>10,566</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1139,78 +1139,78 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,515</t>
+          <t>20,405</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>10,566</t>
+          <t>17,571</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>17,671</t>
+          <t>21,567</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>41,880</t>
+          <t>59,711,247</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1227,56 +1227,56 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>13,105</t>
+          <t>13,005</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>48,100</t>
+          <t>41,650</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>21,687</t>
+          <t>47,840</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>984,130</t>
+          <t>984,134</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>48,705,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1,068,793</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
